--- a/artfynd/A 22901-2026 artfynd.xlsx
+++ b/artfynd/A 22901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>453566</v>
+        <v>401701</v>
       </c>
       <c r="B2" t="n">
-        <v>94531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1452</v>
+        <v>990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Timmerskapania</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scapania apiculata</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Spruce</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608237.3788423839</v>
+        <v>608237</v>
       </c>
       <c r="R2" t="n">
-        <v>6940291.595361052</v>
+        <v>6940292</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,24 +743,9 @@
           <t>2009-08-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4-5 bra stockar vid nedlagd kvar, betongkonstruktion</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +762,14 @@
           <t>Å med nedlagd kvarn, igenvuxet med löv</t>
         </is>
       </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Stockar</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -794,375 +782,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>401701</v>
-      </c>
-      <c r="B3" t="n">
-        <v>94436</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>990</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Liten hornflikmossa</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lophozia ascendens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Kvarnån (Bjässjöån), vid gamla kvarnen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>608237.3788423839</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6940291.595361052</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Indal</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Å med nedlagd kvarn, igenvuxet med löv</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>2 substratenheter # Stockar</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Henrik Weibull, Andreas Karlberg, Jonas Salmonsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>458699</v>
-      </c>
-      <c r="B4" t="n">
-        <v>94520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1845</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Svämskapania</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Scapania glaucocephala</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Taylor) Austin</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kvarnån (Bjässjöån), vid gamla kvarnen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>608237.3788423839</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6940291.595361052</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Indal</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4-5 bra stockar vid nedlagd kvar, betongkonstruktion</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Å med nedlagd kvarn, igenvuxet med löv</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Henrik Weibull, Jonas Salmonsson, Andreas Karlberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>457034</v>
-      </c>
-      <c r="B5" t="n">
-        <v>94521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1455</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Mikroskapania</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Scapania carinthiaca</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>J.B.Jack ex Lindb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kvarnån (Bjässjöån), vid gamla kvarnen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>608237.3788423839</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6940291.595361052</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Indal</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2009-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4-5 bra stockar vid nedlagd kvar, betongkonstruktion</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Å med nedlagd kvarn, igenvuxet med löv</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Henrik Weibull, Andreas Karlberg, Jonas Salmonsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22901-2026 artfynd.xlsx
+++ b/artfynd/A 22901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,8 +787,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/401701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>